--- a/operadores-y-unidades-bimbo-sureste.xlsx
+++ b/operadores-y-unidades-bimbo-sureste.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A2:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,11 @@
   </cols>
   <sheetData>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Operadores y unidades de Bimbo Sureste — validación</t>
+        </is>
+      </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Operadores de Bimbo Sureste — validación</t>
@@ -486,6 +491,11 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Este archivo trae DOS pestañas abajo: «Operadores» y «Unidades». Llena las dos. </t>
+        </is>
+      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Es la lista de operadores que vamos a dar de alta en SU plataforma de Bimbo en Uvicuo. Esta información es la que quedará cargada.</t>
